--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121659474</v>
+        <v>121659476</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504829</v>
+        <v>504914</v>
       </c>
       <c r="R2" t="n">
-        <v>7088169</v>
+        <v>7088158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121659475</v>
+        <v>121659482</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>91290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504879</v>
+        <v>504851</v>
       </c>
       <c r="R3" t="n">
-        <v>7088143</v>
+        <v>7088142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121659480</v>
+        <v>121659479</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +927,7 @@
         <v>505290</v>
       </c>
       <c r="R4" t="n">
-        <v>7088282</v>
+        <v>7088286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121659477</v>
+        <v>121659475</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505143</v>
+        <v>504879</v>
       </c>
       <c r="R5" t="n">
-        <v>7088171</v>
+        <v>7088143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659476</v>
+        <v>121659478</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504914</v>
+        <v>505156</v>
       </c>
       <c r="R6" t="n">
-        <v>7088158</v>
+        <v>7088164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121659478</v>
+        <v>121659480</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505156</v>
+        <v>505290</v>
       </c>
       <c r="R7" t="n">
-        <v>7088164</v>
+        <v>7088282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659482</v>
+        <v>121659474</v>
       </c>
       <c r="B8" t="n">
-        <v>91282</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1324,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504851</v>
+        <v>504829</v>
       </c>
       <c r="R8" t="n">
-        <v>7088142</v>
+        <v>7088169</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659479</v>
+        <v>121659477</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505290</v>
+        <v>505143</v>
       </c>
       <c r="R9" t="n">
-        <v>7088286</v>
+        <v>7088171</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659478</v>
+        <v>121659480</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505156</v>
+        <v>505290</v>
       </c>
       <c r="R6" t="n">
-        <v>7088164</v>
+        <v>7088282</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121659480</v>
+        <v>121659478</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505290</v>
+        <v>505156</v>
       </c>
       <c r="R7" t="n">
-        <v>7088282</v>
+        <v>7088164</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121659475</v>
+        <v>121659474</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504879</v>
+        <v>504829</v>
       </c>
       <c r="R2" t="n">
-        <v>7088143</v>
+        <v>7088169</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121659477</v>
+        <v>121659476</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505143</v>
+        <v>504914</v>
       </c>
       <c r="R3" t="n">
-        <v>7088171</v>
+        <v>7088158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121659479</v>
+        <v>121659478</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505290</v>
+        <v>505156</v>
       </c>
       <c r="R4" t="n">
-        <v>7088286</v>
+        <v>7088164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121659478</v>
+        <v>121659475</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505156</v>
+        <v>504879</v>
       </c>
       <c r="R5" t="n">
-        <v>7088164</v>
+        <v>7088143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659482</v>
+        <v>121659479</v>
       </c>
       <c r="B6" t="n">
-        <v>91290</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504851</v>
+        <v>505290</v>
       </c>
       <c r="R6" t="n">
-        <v>7088142</v>
+        <v>7088286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121659480</v>
+        <v>121659477</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505290</v>
+        <v>505143</v>
       </c>
       <c r="R7" t="n">
-        <v>7088282</v>
+        <v>7088171</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659476</v>
+        <v>121659482</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>91290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504914</v>
+        <v>504851</v>
       </c>
       <c r="R8" t="n">
-        <v>7088158</v>
+        <v>7088142</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659474</v>
+        <v>121659480</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504829</v>
+        <v>505290</v>
       </c>
       <c r="R9" t="n">
-        <v>7088169</v>
+        <v>7088282</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659482</v>
+        <v>121659480</v>
       </c>
       <c r="B8" t="n">
-        <v>91290</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504851</v>
+        <v>505290</v>
       </c>
       <c r="R8" t="n">
-        <v>7088142</v>
+        <v>7088282</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659480</v>
+        <v>121659482</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>91290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,25 +1436,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505290</v>
+        <v>504851</v>
       </c>
       <c r="R9" t="n">
-        <v>7088282</v>
+        <v>7088142</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121659474</v>
+        <v>121659478</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504829</v>
+        <v>505156</v>
       </c>
       <c r="R2" t="n">
-        <v>7088169</v>
+        <v>7088164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121659476</v>
+        <v>121659482</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>91290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504914</v>
+        <v>504851</v>
       </c>
       <c r="R3" t="n">
-        <v>7088158</v>
+        <v>7088142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121659478</v>
+        <v>121659474</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505156</v>
+        <v>504829</v>
       </c>
       <c r="R4" t="n">
-        <v>7088164</v>
+        <v>7088169</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121659475</v>
+        <v>121659477</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504879</v>
+        <v>505143</v>
       </c>
       <c r="R5" t="n">
-        <v>7088143</v>
+        <v>7088171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659479</v>
+        <v>121659475</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505290</v>
+        <v>504879</v>
       </c>
       <c r="R6" t="n">
-        <v>7088286</v>
+        <v>7088143</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121659477</v>
+        <v>121659480</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505143</v>
+        <v>505290</v>
       </c>
       <c r="R7" t="n">
-        <v>7088171</v>
+        <v>7088282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659480</v>
+        <v>121659479</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1360,7 +1355,7 @@
         <v>505290</v>
       </c>
       <c r="R8" t="n">
-        <v>7088282</v>
+        <v>7088286</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659482</v>
+        <v>121659476</v>
       </c>
       <c r="B9" t="n">
-        <v>91290</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,25 +1431,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504851</v>
+        <v>504914</v>
       </c>
       <c r="R9" t="n">
-        <v>7088142</v>
+        <v>7088158</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121659478</v>
+        <v>121659475</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505156</v>
+        <v>504879</v>
       </c>
       <c r="R2" t="n">
-        <v>7088164</v>
+        <v>7088143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121659482</v>
+        <v>121659480</v>
       </c>
       <c r="B3" t="n">
-        <v>91290</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504851</v>
+        <v>505290</v>
       </c>
       <c r="R3" t="n">
-        <v>7088142</v>
+        <v>7088282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121659474</v>
+        <v>121659479</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504829</v>
+        <v>505290</v>
       </c>
       <c r="R4" t="n">
-        <v>7088169</v>
+        <v>7088286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121659477</v>
+        <v>121659482</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>91290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505143</v>
+        <v>504851</v>
       </c>
       <c r="R5" t="n">
-        <v>7088171</v>
+        <v>7088142</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659475</v>
+        <v>121659474</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504879</v>
+        <v>504829</v>
       </c>
       <c r="R6" t="n">
-        <v>7088143</v>
+        <v>7088169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121659480</v>
+        <v>121659476</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505290</v>
+        <v>504914</v>
       </c>
       <c r="R7" t="n">
-        <v>7088282</v>
+        <v>7088158</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659479</v>
+        <v>121659477</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505290</v>
+        <v>505143</v>
       </c>
       <c r="R8" t="n">
-        <v>7088286</v>
+        <v>7088171</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659476</v>
+        <v>121659478</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504914</v>
+        <v>505156</v>
       </c>
       <c r="R9" t="n">
-        <v>7088158</v>
+        <v>7088164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121659475</v>
+        <v>121659478</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504879</v>
+        <v>505156</v>
       </c>
       <c r="R2" t="n">
-        <v>7088143</v>
+        <v>7088164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121659480</v>
+        <v>121659476</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505290</v>
+        <v>504914</v>
       </c>
       <c r="R3" t="n">
-        <v>7088282</v>
+        <v>7088158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121659479</v>
+        <v>121659474</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505290</v>
+        <v>504829</v>
       </c>
       <c r="R4" t="n">
-        <v>7088286</v>
+        <v>7088169</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121659482</v>
+        <v>121659480</v>
       </c>
       <c r="B5" t="n">
-        <v>91290</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504851</v>
+        <v>505290</v>
       </c>
       <c r="R5" t="n">
-        <v>7088142</v>
+        <v>7088282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659474</v>
+        <v>121659477</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504829</v>
+        <v>505143</v>
       </c>
       <c r="R6" t="n">
-        <v>7088169</v>
+        <v>7088171</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121659476</v>
+        <v>121659475</v>
       </c>
       <c r="B7" t="n">
         <v>57357</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504914</v>
+        <v>504879</v>
       </c>
       <c r="R7" t="n">
-        <v>7088158</v>
+        <v>7088143</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659477</v>
+        <v>121659482</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>91290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505143</v>
+        <v>504851</v>
       </c>
       <c r="R8" t="n">
-        <v>7088171</v>
+        <v>7088142</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659478</v>
+        <v>121659479</v>
       </c>
       <c r="B9" t="n">
         <v>57357</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505156</v>
+        <v>505290</v>
       </c>
       <c r="R9" t="n">
-        <v>7088164</v>
+        <v>7088286</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121659478</v>
+        <v>121659480</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505156</v>
+        <v>505290</v>
       </c>
       <c r="R2" t="n">
-        <v>7088164</v>
+        <v>7088282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121659476</v>
+        <v>121659477</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504914</v>
+        <v>505143</v>
       </c>
       <c r="R3" t="n">
-        <v>7088158</v>
+        <v>7088171</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121659474</v>
+        <v>121659476</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504829</v>
+        <v>504914</v>
       </c>
       <c r="R4" t="n">
-        <v>7088169</v>
+        <v>7088158</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121659480</v>
+        <v>121659478</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505290</v>
+        <v>505156</v>
       </c>
       <c r="R5" t="n">
-        <v>7088282</v>
+        <v>7088164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659477</v>
+        <v>121659479</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505143</v>
+        <v>505290</v>
       </c>
       <c r="R6" t="n">
-        <v>7088171</v>
+        <v>7088286</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659482</v>
+        <v>121659474</v>
       </c>
       <c r="B8" t="n">
-        <v>91290</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504851</v>
+        <v>504829</v>
       </c>
       <c r="R8" t="n">
-        <v>7088142</v>
+        <v>7088169</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659479</v>
+        <v>121659482</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>91290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,25 +1436,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505290</v>
+        <v>504851</v>
       </c>
       <c r="R9" t="n">
-        <v>7088286</v>
+        <v>7088142</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121659480</v>
+        <v>121659477</v>
       </c>
       <c r="B2" t="n">
         <v>57357</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505290</v>
+        <v>505143</v>
       </c>
       <c r="R2" t="n">
-        <v>7088282</v>
+        <v>7088171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121659477</v>
+        <v>121659480</v>
       </c>
       <c r="B3" t="n">
         <v>57357</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505143</v>
+        <v>505290</v>
       </c>
       <c r="R3" t="n">
-        <v>7088171</v>
+        <v>7088282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121659476</v>
+        <v>121659482</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>91290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504914</v>
+        <v>504851</v>
       </c>
       <c r="R4" t="n">
-        <v>7088158</v>
+        <v>7088142</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121659478</v>
+        <v>121659474</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505156</v>
+        <v>504829</v>
       </c>
       <c r="R5" t="n">
-        <v>7088164</v>
+        <v>7088169</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659479</v>
+        <v>121659478</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505290</v>
+        <v>505156</v>
       </c>
       <c r="R6" t="n">
-        <v>7088286</v>
+        <v>7088164</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659474</v>
+        <v>121659476</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504829</v>
+        <v>504914</v>
       </c>
       <c r="R8" t="n">
-        <v>7088169</v>
+        <v>7088158</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659482</v>
+        <v>121659479</v>
       </c>
       <c r="B9" t="n">
-        <v>91290</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,25 +1431,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504851</v>
+        <v>505290</v>
       </c>
       <c r="R9" t="n">
-        <v>7088142</v>
+        <v>7088286</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121659477</v>
+        <v>121659480</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505143</v>
+        <v>505290</v>
       </c>
       <c r="R2" t="n">
-        <v>7088171</v>
+        <v>7088282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121659480</v>
+        <v>121659479</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>505290</v>
       </c>
       <c r="R3" t="n">
-        <v>7088282</v>
+        <v>7088286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121659482</v>
+        <v>121659475</v>
       </c>
       <c r="B4" t="n">
-        <v>91290</v>
+        <v>57365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504851</v>
+        <v>504879</v>
       </c>
       <c r="R4" t="n">
-        <v>7088142</v>
+        <v>7088143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +999,7 @@
         <v>121659474</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659478</v>
+        <v>121659482</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>91304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505156</v>
+        <v>504851</v>
       </c>
       <c r="R6" t="n">
-        <v>7088164</v>
+        <v>7088142</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121659475</v>
+        <v>121659476</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504879</v>
+        <v>504914</v>
       </c>
       <c r="R7" t="n">
-        <v>7088143</v>
+        <v>7088158</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659476</v>
+        <v>121659478</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504914</v>
+        <v>505156</v>
       </c>
       <c r="R8" t="n">
-        <v>7088158</v>
+        <v>7088164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659479</v>
+        <v>121659477</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505290</v>
+        <v>505143</v>
       </c>
       <c r="R9" t="n">
-        <v>7088286</v>
+        <v>7088171</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121659479</v>
+        <v>121659476</v>
       </c>
       <c r="B3" t="n">
         <v>57365</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505290</v>
+        <v>504914</v>
       </c>
       <c r="R3" t="n">
-        <v>7088286</v>
+        <v>7088158</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121659475</v>
+        <v>121659478</v>
       </c>
       <c r="B4" t="n">
         <v>57365</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504879</v>
+        <v>505156</v>
       </c>
       <c r="R4" t="n">
-        <v>7088143</v>
+        <v>7088164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121659474</v>
+        <v>121659477</v>
       </c>
       <c r="B5" t="n">
         <v>57365</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504829</v>
+        <v>505143</v>
       </c>
       <c r="R5" t="n">
-        <v>7088169</v>
+        <v>7088171</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659482</v>
+        <v>121659475</v>
       </c>
       <c r="B6" t="n">
-        <v>91304</v>
+        <v>57365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504851</v>
+        <v>504879</v>
       </c>
       <c r="R6" t="n">
-        <v>7088142</v>
+        <v>7088143</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121659476</v>
+        <v>121659482</v>
       </c>
       <c r="B7" t="n">
-        <v>57365</v>
+        <v>91306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504914</v>
+        <v>504851</v>
       </c>
       <c r="R7" t="n">
-        <v>7088158</v>
+        <v>7088142</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659478</v>
+        <v>121659474</v>
       </c>
       <c r="B8" t="n">
         <v>57365</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505156</v>
+        <v>504829</v>
       </c>
       <c r="R8" t="n">
-        <v>7088164</v>
+        <v>7088169</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659477</v>
+        <v>121659479</v>
       </c>
       <c r="B9" t="n">
         <v>57365</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505143</v>
+        <v>505290</v>
       </c>
       <c r="R9" t="n">
-        <v>7088171</v>
+        <v>7088286</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49646-2024 artfynd.xlsx
+++ b/artfynd/A 49646-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121659476</v>
+        <v>121659477</v>
       </c>
       <c r="B3" t="n">
         <v>57365</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504914</v>
+        <v>505143</v>
       </c>
       <c r="R3" t="n">
-        <v>7088158</v>
+        <v>7088171</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121659478</v>
+        <v>121659476</v>
       </c>
       <c r="B4" t="n">
         <v>57365</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505156</v>
+        <v>504914</v>
       </c>
       <c r="R4" t="n">
-        <v>7088164</v>
+        <v>7088158</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121659477</v>
+        <v>121659474</v>
       </c>
       <c r="B5" t="n">
         <v>57365</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505143</v>
+        <v>504829</v>
       </c>
       <c r="R5" t="n">
-        <v>7088171</v>
+        <v>7088169</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121659475</v>
+        <v>121659482</v>
       </c>
       <c r="B6" t="n">
-        <v>57365</v>
+        <v>91307</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504879</v>
+        <v>504851</v>
       </c>
       <c r="R6" t="n">
-        <v>7088143</v>
+        <v>7088142</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121659482</v>
+        <v>121659478</v>
       </c>
       <c r="B7" t="n">
-        <v>91306</v>
+        <v>57365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504851</v>
+        <v>505156</v>
       </c>
       <c r="R7" t="n">
-        <v>7088142</v>
+        <v>7088164</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121659474</v>
+        <v>121659479</v>
       </c>
       <c r="B8" t="n">
         <v>57365</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504829</v>
+        <v>505290</v>
       </c>
       <c r="R8" t="n">
-        <v>7088169</v>
+        <v>7088286</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121659479</v>
+        <v>121659475</v>
       </c>
       <c r="B9" t="n">
         <v>57365</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505290</v>
+        <v>504879</v>
       </c>
       <c r="R9" t="n">
-        <v>7088286</v>
+        <v>7088143</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
